--- a/utils/monday_sprint_sprint_2023-20.xlsx
+++ b/utils/monday_sprint_sprint_2023-20.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="198">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>19839</t>
+    <t>5123169272</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>07/09/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>05/10/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>21887</t>
+    <t>5216335316</t>
   </si>
   <si>
     <t>Melhoria Sistema Tratamento Termico - Gerar Excel</t>
@@ -111,10 +111,13 @@
     <t>25/09/2023</t>
   </si>
   <si>
+    <t>03/10/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>21928</t>
+    <t>5053616050</t>
   </si>
   <si>
     <t>Inventário por cliente - Expedição</t>
@@ -126,7 +129,7 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>22316</t>
+    <t>5209596649</t>
   </si>
   <si>
     <t>Habilitar opção de colar - Tela Orçamento</t>
@@ -135,13 +138,19 @@
     <t>22/09/2023</t>
   </si>
   <si>
-    <t>22326</t>
+    <t>08/10/2023</t>
+  </si>
+  <si>
+    <t>5209537028</t>
   </si>
   <si>
     <t>CBO - Posto de cópia eletrônico</t>
   </si>
   <si>
-    <t>22037</t>
+    <t>24/09/2023</t>
+  </si>
+  <si>
+    <t>5064964665</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -156,103 +165,115 @@
     <t>28/08/2023</t>
   </si>
   <si>
-    <t>22291</t>
+    <t>5209862360</t>
   </si>
   <si>
     <t>Adição de formulário de temperatura</t>
   </si>
   <si>
-    <t>22442</t>
+    <t>28/09/2023</t>
+  </si>
+  <si>
+    <t>5209247793</t>
   </si>
   <si>
     <t>Relatório XML não lançados</t>
   </si>
   <si>
-    <t>22275</t>
+    <t>5209906226</t>
   </si>
   <si>
     <t>Relatório de Estoque PA Congelado</t>
   </si>
   <si>
-    <t>22419</t>
+    <t>26/09/2023</t>
+  </si>
+  <si>
+    <t>5209268144</t>
   </si>
   <si>
     <t>Melhorias Sistema de Apontamentos Moldagem USE</t>
   </si>
   <si>
-    <t>22280</t>
+    <t>5209918623</t>
   </si>
   <si>
     <t>Alterações no sistema de manutenção 3</t>
   </si>
   <si>
-    <t>22417</t>
+    <t>5209278503</t>
   </si>
   <si>
     <t>Alterações no sistema de manutenção 1</t>
   </si>
   <si>
-    <t>22254</t>
+    <t>5209932257</t>
   </si>
   <si>
     <t>Alteração Tela Registro de Fechamento UPR</t>
   </si>
   <si>
-    <t>22232</t>
+    <t>5210020554</t>
   </si>
   <si>
     <t>LIBERAR ACESSO</t>
   </si>
   <si>
-    <t>22383</t>
+    <t>5209336415</t>
   </si>
   <si>
     <t>Movimentação em lote - Expedição</t>
   </si>
   <si>
-    <t>22464</t>
+    <t>5221068663</t>
   </si>
   <si>
     <t>Ajuste Sistema de Logística Interna</t>
   </si>
   <si>
-    <t>22370</t>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>5209396107</t>
   </si>
   <si>
     <t>Controle da aderência - Usinagem Final</t>
   </si>
   <si>
-    <t>22358</t>
+    <t>5209407167</t>
   </si>
   <si>
     <t>[SUPRIMENTOS] Melhoria tela de recebimento fiscal (CORREÇÃO - lançamento OC 327765)</t>
   </si>
   <si>
-    <t>22353</t>
+    <t>07/10/2023</t>
+  </si>
+  <si>
+    <t>5209455680</t>
   </si>
   <si>
     <t>Valorização dentro do Planilhão - USE + UPR</t>
   </si>
   <si>
-    <t>22344</t>
+    <t>5209481993</t>
   </si>
   <si>
     <t>Projeto FATURA - Erro de informação de data original no planilhão</t>
   </si>
   <si>
-    <t>22340</t>
+    <t>5209500524</t>
   </si>
   <si>
     <t>NOVO FILTRO PARA EXPORTAÇÃO SISTEMA DE CORRIDAS</t>
   </si>
   <si>
-    <t>22008</t>
+    <t>5210705198</t>
   </si>
   <si>
     <t>Evento recusa automatico</t>
   </si>
   <si>
-    <t>22237</t>
+    <t>5209963777</t>
   </si>
   <si>
     <t>Correção</t>
@@ -261,16 +282,13 @@
     <t>Preenchimento de Maquina Parada</t>
   </si>
   <si>
-    <t>22443</t>
+    <t>5224633162</t>
   </si>
   <si>
     <t>Sistema desmoldagem - habilitar ressalva</t>
   </si>
   <si>
-    <t>26/09/2023</t>
-  </si>
-  <si>
-    <t>18941</t>
+    <t>4983532426</t>
   </si>
   <si>
     <t>Produtivo em horas</t>
@@ -279,34 +297,34 @@
     <t>14/08/2023</t>
   </si>
   <si>
+    <t>13/08/2023</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>22014</t>
+    <t>5217153929</t>
   </si>
   <si>
     <t>Integração NIMBI x ERP Altona (Itens de estoque)</t>
   </si>
   <si>
-    <t>22382</t>
+    <t>5209352075</t>
   </si>
   <si>
     <t>SISTEMA EXPEDIÇÃO</t>
   </si>
   <si>
-    <t>22293</t>
+    <t>5209854386</t>
   </si>
   <si>
     <t>Melhoria no sistema Ensaios Destrutivos</t>
   </si>
   <si>
-    <t>21798</t>
+    <t>5070226589</t>
   </si>
   <si>
     <t>TABLET´S AJUSTAGEM</t>
@@ -318,70 +336,127 @@
     <t>Semana 5</t>
   </si>
   <si>
+    <t>5219550050</t>
+  </si>
+  <si>
     <t>Atualizar do material no NIMBI</t>
   </si>
   <si>
+    <t>5219569001</t>
+  </si>
+  <si>
     <t>Integrar fornecedor (já cadastrado no ERP)</t>
   </si>
   <si>
+    <t>5219575167</t>
+  </si>
+  <si>
     <t>Receber fornecedor (Receber fornecedor novo)</t>
   </si>
   <si>
+    <t>5219578037</t>
+  </si>
+  <si>
     <t>Receber processo</t>
   </si>
   <si>
+    <t>5219580775</t>
+  </si>
+  <si>
     <t>Receber itens do processo</t>
   </si>
   <si>
-    <t>22466</t>
+    <t>09/10/2023</t>
+  </si>
+  <si>
+    <t>5220858920</t>
   </si>
   <si>
     <t>Validação Ajustagem em tablets</t>
   </si>
   <si>
+    <t>5221009758</t>
+  </si>
+  <si>
     <t>Alterar o label para “Adicionar”</t>
   </si>
   <si>
+    <t>5221041478</t>
+  </si>
+  <si>
     <t>Colocar o campo de quantidade no segundo nivel</t>
   </si>
   <si>
+    <t>5221047392</t>
+  </si>
+  <si>
     <t>Incluir nome do apontador no rodapé da página</t>
   </si>
   <si>
+    <t>5210621873</t>
+  </si>
+  <si>
     <t>Melhoria na visualização dos romaneios</t>
   </si>
   <si>
+    <t>5221049413</t>
+  </si>
+  <si>
     <t>Verificar títulos das telas</t>
   </si>
   <si>
+    <t>5221055750</t>
+  </si>
+  <si>
     <t>Criar tela de consulta de apontamentos não finalizados</t>
   </si>
   <si>
-    <t>22372</t>
+    <t>5209371644</t>
   </si>
   <si>
     <t>Alterações no sistema de manutenção 2</t>
   </si>
   <si>
+    <t>5210632719</t>
+  </si>
+  <si>
     <t>Melhoria entrada no depósito</t>
   </si>
   <si>
+    <t>5210643087</t>
+  </si>
+  <si>
     <t>Melhoria consulta romaneio</t>
   </si>
   <si>
+    <t>5210655555</t>
+  </si>
+  <si>
     <t>Correção em inventário x Box</t>
   </si>
   <si>
+    <t>5210649469</t>
+  </si>
+  <si>
     <t>Melhoria em editar romaneio</t>
   </si>
   <si>
+    <t>27/09/2023</t>
+  </si>
+  <si>
+    <t>5210670046</t>
+  </si>
+  <si>
     <t>VALIDAR O SISTEMA DE SAIDA DEPOSITO</t>
   </si>
   <si>
+    <t>5210664401</t>
+  </si>
+  <si>
     <t>Melhoria consulta saldo de deposito</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>5249413209</t>
   </si>
   <si>
     <t>Criar campos nas tabelas de de check list e movimentação de peças</t>
@@ -390,18 +465,30 @@
     <t>29/09/2023</t>
   </si>
   <si>
+    <t>5249416138</t>
+  </si>
+  <si>
     <t>Atualizar rotinas da analise critica para revisão de documentos</t>
   </si>
   <si>
+    <t>5249423055</t>
+  </si>
+  <si>
     <t>Atualizar movimentação do pré produtivo para revisão de documentos</t>
   </si>
   <si>
+    <t>5312775107</t>
+  </si>
+  <si>
     <t>Projeto FATURA - Erro de informação de data original no planilhão - Fechamento</t>
   </si>
   <si>
     <t>11/10/2023</t>
   </si>
   <si>
+    <t>10/10/2023</t>
+  </si>
+  <si>
     <t>Outubro</t>
   </si>
   <si>
@@ -423,19 +510,22 @@
     <t>5219213076</t>
   </si>
   <si>
-    <t>22384</t>
+    <t>5209320697</t>
   </si>
   <si>
     <t>Melhorias Sistemas de Custeio - Apoios de Custo</t>
   </si>
   <si>
+    <t>04/10/2023</t>
+  </si>
+  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-20</t>
+    <t>Ago/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -1077,7 +1167,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1086,7 +1176,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -1094,7 +1184,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1106,10 +1196,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1121,7 +1211,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -1133,15 +1223,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1153,10 +1243,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1168,10 +1258,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1180,7 +1270,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1188,7 +1278,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1200,10 +1290,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1215,10 +1305,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1227,7 +1317,7 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1235,25 +1325,25 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1262,10 +1352,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1274,15 +1364,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1294,10 +1384,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1309,10 +1399,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1321,7 +1411,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -1329,7 +1419,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1341,10 +1431,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1356,10 +1446,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1368,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -1376,7 +1466,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1388,10 +1478,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1403,10 +1493,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1415,7 +1505,7 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -1423,7 +1513,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1435,10 +1525,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1450,10 +1540,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1462,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1470,7 +1560,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1482,10 +1572,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1497,7 +1587,7 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>24</v>
@@ -1509,7 +1599,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>28</v>
@@ -1517,7 +1607,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1529,10 +1619,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1544,7 +1634,7 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>24</v>
@@ -1556,7 +1646,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1564,7 +1654,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1576,10 +1666,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1591,10 +1681,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1603,7 +1693,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1611,7 +1701,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1623,10 +1713,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1638,10 +1728,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1650,7 +1740,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -1658,7 +1748,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1670,10 +1760,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1685,7 +1775,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1697,7 +1787,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -1705,7 +1795,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1717,10 +1807,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1735,7 +1825,7 @@
         <v>31</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1744,7 +1834,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -1752,7 +1842,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1764,10 +1854,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1779,10 +1869,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1791,7 +1881,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -1799,7 +1889,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1811,10 +1901,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1826,10 +1916,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1838,7 +1928,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1846,7 +1936,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1858,10 +1948,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1873,10 +1963,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1885,7 +1975,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -1893,22 +1983,22 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1920,10 +2010,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1932,7 +2022,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -1940,7 +2030,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1952,10 +2042,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1967,10 +2057,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1979,7 +2069,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -1987,7 +2077,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1999,10 +2089,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2014,10 +2104,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2026,7 +2116,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -2034,22 +2124,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2061,10 +2151,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2073,7 +2163,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2081,7 +2171,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2093,10 +2183,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2108,10 +2198,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2120,7 +2210,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2128,7 +2218,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2140,13 +2230,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2155,45 +2245,45 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2205,16 +2295,16 @@
         <v>31</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2222,7 +2312,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2234,10 +2324,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2249,19 +2339,19 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2269,7 +2359,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2281,10 +2371,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2296,7 +2386,7 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
@@ -2308,7 +2398,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2316,22 +2406,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2343,10 +2433,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2355,33 +2445,33 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2402,7 +2492,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2410,25 +2500,25 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2449,7 +2539,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2457,25 +2547,25 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2496,7 +2586,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2504,25 +2594,25 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>21</v>
@@ -2543,7 +2633,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2551,25 +2641,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>21</v>
@@ -2581,7 +2671,7 @@
         <v>31</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2590,7 +2680,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2598,7 +2688,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2610,10 +2700,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2637,7 +2727,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -2645,7 +2735,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2657,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2675,7 +2765,7 @@
         <v>31</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2684,7 +2774,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -2692,7 +2782,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2704,10 +2794,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2722,7 +2812,7 @@
         <v>31</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2731,7 +2821,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2739,7 +2829,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2751,10 +2841,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2769,7 +2859,7 @@
         <v>31</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2778,7 +2868,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -2786,25 +2876,25 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>21</v>
@@ -2813,10 +2903,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2825,7 +2915,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -2833,7 +2923,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2845,10 +2935,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2863,7 +2953,7 @@
         <v>31</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2872,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2880,7 +2970,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2892,10 +2982,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2910,7 +3000,7 @@
         <v>31</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2919,7 +3009,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2927,7 +3017,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2939,10 +3029,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2954,7 +3044,7 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
@@ -2966,7 +3056,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2974,22 +3064,22 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3001,10 +3091,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3013,7 +3103,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3021,22 +3111,22 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3048,10 +3138,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3060,7 +3150,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3068,22 +3158,22 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3095,10 +3185,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3107,7 +3197,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3115,22 +3205,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3142,10 +3232,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3154,7 +3244,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3162,22 +3252,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3189,7 +3279,7 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>24</v>
@@ -3201,7 +3291,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3209,22 +3299,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3236,10 +3326,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3248,7 +3338,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3256,7 +3346,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3268,10 +3358,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3283,10 +3373,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3295,7 +3385,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3303,7 +3393,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3315,10 +3405,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3330,10 +3420,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3342,7 +3432,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3350,7 +3440,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3362,10 +3452,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3377,10 +3467,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3389,7 +3479,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -3397,22 +3487,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3424,45 +3514,45 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>21</v>
@@ -3474,7 +3564,7 @@
         <v>31</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3483,7 +3573,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -3491,25 +3581,25 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>21</v>
@@ -3521,7 +3611,7 @@
         <v>31</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3530,7 +3620,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -3538,25 +3628,25 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>21</v>
@@ -3568,7 +3658,7 @@
         <v>31</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3577,7 +3667,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3585,7 +3675,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3597,10 +3687,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3612,10 +3702,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3624,7 +3714,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -3643,23 +3733,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3667,16 +3757,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3687,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>11.52</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3695,7 +3785,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3708,7 +3798,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3716,7 +3806,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3747,12 +3837,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="B2">
         <v>56</v>
@@ -3766,7 +3856,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3776,25 +3866,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3811,13 +3901,13 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3832,18 +3922,18 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -3852,24 +3942,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M11" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="N11">
         <v>4</v>
       </c>
       <c r="P11" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="Q11">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -3881,39 +3971,39 @@
         <v>44</v>
       </c>
       <c r="J12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3921,13 +4011,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3935,7 +4025,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3943,7 +4033,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3951,7 +4041,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3959,10 +4049,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3970,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3978,142 +4068,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>164</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
